--- a/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27fcda80d8bb479c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49c0fbd7a1f24cb2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49c0fbd7a1f24cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f1b97d9e6da4e99"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f1b97d9e6da4e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95e45d2e0eb24838"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95e45d2e0eb24838"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d09ae89099440c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d09ae89099440c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f0c026c796342c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f0c026c796342c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra48895a05f3346aa"/>
   </x:sheets>
 </x:workbook>
 </file>
